--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/cash_positioning.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/cash_positioning.xlsx
@@ -478,14 +478,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>399.9</v>
+        <v>303.6</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>DBS</t>
         </is>
       </c>
     </row>
@@ -496,14 +496,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>297.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>27.4</v>
+        <v>119.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>DBS</t>
         </is>
       </c>
     </row>
@@ -514,14 +514,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.3</v>
+        <v>216</v>
       </c>
       <c r="C5" t="n">
-        <v>96.59999999999999</v>
+        <v>17.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>DBS</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>203.1</v>
+        <v>299.2</v>
       </c>
       <c r="C6" t="n">
-        <v>90.8</v>
+        <v>83.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>JPMorgan</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.5</v>
+        <v>183.9</v>
       </c>
       <c r="C7" t="n">
-        <v>55.6</v>
+        <v>65.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.7</v>
+        <v>211.5</v>
       </c>
       <c r="C8" t="n">
-        <v>32.6</v>
+        <v>39.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.7</v>
+        <v>364.5</v>
       </c>
       <c r="C9" t="n">
-        <v>89.2</v>
+        <v>0.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>304.1</v>
+        <v>327.2</v>
       </c>
       <c r="C10" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>Citi</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>133.7</v>
+        <v>142.9</v>
       </c>
       <c r="C11" t="n">
-        <v>12.3</v>
+        <v>88.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>289.1</v>
+        <v>149.2</v>
       </c>
       <c r="C12" t="n">
-        <v>13.7</v>
+        <v>21.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
